--- a/data/S1987_88_FINAL.xlsx
+++ b/data/S1987_88_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$14</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +81,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,12 +99,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -23877,7 +23895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23921,6 +23939,162 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1987_88_0036 'Gumárne 1. mája Púchov' prev→CLUB_S1986_87_0083 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1987_88_0254 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1987_88_0255 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1987_88_0256 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1987_88_0464 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1987_88_0465 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1987_88_0466 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1987_88_0467 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1987_88_0468 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1987_88_0469 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1987_88_0470 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1987_88_0471 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] fate: CLUB_S1987_88_0472 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -29556,8 +29730,6 @@
         </is>
       </c>
     </row>
-    <row r="135"/>
-    <row r="136"/>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
@@ -29637,7 +29809,6 @@
         </is>
       </c>
     </row>
-    <row r="144"/>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
@@ -57179,6 +57350,347 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0036</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0036 'Gumárne 1. mája Púchov' prev→CLUB_S1986_87_0083 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0254</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0254 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0255</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0255 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0256</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0256 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0464</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0464 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0465</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0465 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0466</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0466 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0467</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0467 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0468</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0468 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0469</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0469 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0470</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0470 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0471</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0471 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>fate</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0472</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0472 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F14"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1987_88_FINAL.xlsx
+++ b/data/S1987_88_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5747,6 +5747,11 @@
           <t>CLUB_S1986_87_0335</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V46" t="inlineStr">
         <is>
           <t>TR_S1987_88_00271</t>
@@ -23895,7 +23900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23945,7 +23950,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1987_88_0036 'Gumárne 1. mája Púchov' prev→CLUB_S1986_87_0083 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -23957,7 +23962,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1987_88_0254 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -23969,7 +23974,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1987_88_0255 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -23981,7 +23986,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1987_88_0256 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -23993,7 +23998,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1987_88_0464 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -24005,7 +24010,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1987_88_0465 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -24017,7 +24022,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1987_88_0466 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -24029,7 +24034,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1987_88_0467 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1986_87_0083 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -24041,7 +24046,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1987_88_0468 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -24053,7 +24058,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1987_88_0469 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -24065,7 +24070,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1987_88_0470 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -24077,7 +24082,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1987_88_0471 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -24089,10 +24094,652 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] fate: CLUB_S1987_88_0472 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'JZD Stráž míru Řenče' → 'Řenče' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Stadion Cheb' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0024</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0025</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0026</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0027</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Slovensko'</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0028</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0029</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -29730,6 +30377,8 @@
         </is>
       </c>
     </row>
+    <row r="135"/>
+    <row r="136"/>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
@@ -29760,6 +30409,11 @@
           <t>I.ČNHL (12 CZ) + SNHL (12 SVK)</t>
         </is>
       </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0001</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -29772,6 +30426,11 @@
           <t>Kvalifikace o II.ligu</t>
         </is>
       </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0003</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -29784,6 +30443,11 @@
           <t>Krajské přebory (nové velké kraje!)</t>
         </is>
       </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0003</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -29796,6 +30460,11 @@
           <t>I.třída / I.B třída / Krajská soutěž</t>
         </is>
       </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0037</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -29809,6 +30478,7 @@
         </is>
       </c>
     </row>
+    <row r="144"/>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
@@ -31797,12 +32467,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -32395,12 +33065,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -32689,12 +33359,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -32731,12 +33401,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -32773,12 +33443,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -32983,12 +33653,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -33025,12 +33695,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -33551,12 +34221,12 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -34386,12 +35056,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -34601,12 +35271,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -34643,12 +35313,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -34947,12 +35617,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -35508,12 +36178,12 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky.</t>
+          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky. || TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Lokomotiva Nové Zámky</t>
+          <t>Nové Zámky</t>
         </is>
       </c>
     </row>
@@ -35550,12 +36220,12 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -37137,12 +37807,12 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -38767,12 +39437,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -38893,12 +39563,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -38935,12 +39605,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -39024,12 +39694,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -39197,12 +39867,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -39573,12 +40243,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -39761,12 +40431,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -40226,12 +40896,12 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -40273,12 +40943,12 @@
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -40362,12 +41032,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -40414,12 +41084,12 @@
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -42477,12 +43147,12 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>Řenče = TJ JZD Stráž míru Řenče (Wiki D42 - registr ustavy 04/2026). Plzensky kraj (okres Plzen-jih). JZD 'Stráž míru' = pojmenovani druzstva. city Řenče.</t>
+          <t>Řenče = TJ JZD Stráž míru Řenče (Wiki D42 - registr ustavy 04/2026). Plzensky kraj (okres Plzen-jih). JZD 'Stráž míru' = pojmenovani druzstva. city Řenče. || TBD: city 'JZD Stráž míru Řenče' → 'Řenče' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>JZD Stráž míru Řenče</t>
+          <t>Řenče</t>
         </is>
       </c>
     </row>
@@ -43112,12 +43782,12 @@
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J257" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -43379,12 +44049,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Stadion Cheb' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Stadion Cheb</t>
         </is>
       </c>
     </row>
@@ -44185,12 +44855,12 @@
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J281" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -44432,12 +45102,12 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Dolní Poustevna = TJ Centroflor Dolní Poustevna (Wiki D42 - registr ustavy 04/2026). PARSING CHYBA: 'Pustevna' = preklep z 'Poustevna'. Severocesky/Ustecky kraj (okres Decin). city Dolní Poustevna.</t>
+          <t>Dolní Poustevna = TJ Centroflor Dolní Poustevna (Wiki D42 - registr ustavy 04/2026). PARSING CHYBA: 'Pustevna' = preklep z 'Poustevna'. Severocesky/Ustecky kraj (okres Decin). city Dolní Poustevna. || TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Centroflor Dolní Pustevna</t>
+          <t>Dolní Pustevna</t>
         </is>
       </c>
     </row>
@@ -44484,12 +45154,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -44531,12 +45201,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor.</t>
+          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor. || TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Crystalex 08 Nový Bor</t>
+          <t>Nový Bor</t>
         </is>
       </c>
     </row>
@@ -44630,12 +45300,12 @@
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>Hrádek nL Nisou = TJ ČSAD Hrádek nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Liberec). **ČSAD** = Československá státní automobilová doprava. **Hrádek nL Nisou** = pohranicni mesto trojmezi (CR-DDR/Polsko-NSR). city Hrádek nad Nisou.</t>
+          <t>Hrádek nL Nisou = TJ ČSAD Hrádek nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Liberec). **ČSAD** = Československá státní automobilová doprava. **Hrádek nL Nisou** = pohranicni mesto trojmezi (CR-DDR/Polsko-NSR). city Hrádek nad Nisou. || TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J291" t="inlineStr">
         <is>
-          <t>ČSAD Hrádek nad Nisou</t>
+          <t>Hrádek nad Nisou</t>
         </is>
       </c>
     </row>
@@ -44677,12 +45347,12 @@
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J292" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -44724,12 +45394,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor.</t>
+          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor. || TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Crystalex 08 Nový Bor</t>
+          <t>Nový Bor</t>
         </is>
       </c>
     </row>
@@ -44818,12 +45488,12 @@
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J295" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -45006,12 +45676,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -45152,12 +45822,12 @@
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J302" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -45953,12 +46623,12 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -48509,12 +49179,12 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -48850,12 +49520,12 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -49369,12 +50039,12 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>Veverská Bítýška = TJ RICO Veverská Bítýška (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). **RICO** = pojmenovani po vyrobci (rychlosvyrabne ucely?). NE Veverí (mestska cast Brna), NE Bystřice u Veveří. city Veverská Bítýška.</t>
+          <t>Veverská Bítýška = TJ RICO Veverská Bítýška (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). **RICO** = pojmenovani po vyrobci (rychlosvyrabne ucely?). NE Veverí (mestska cast Brna), NE Bystřice u Veveří. city Veverská Bítýška. || TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>RICO Veverská Bítýška</t>
+          <t>Veverská Bítýška</t>
         </is>
       </c>
     </row>
@@ -50056,12 +50726,12 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -51339,12 +52009,12 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>Ostrava = TJ Hutní Montáže Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Patterns: HM Ostrava. city Ostrava.</t>
+          <t>Ostrava = TJ Hutní Montáže Ostrava (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. Patterns: HM Ostrava. city Ostrava. || TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>Hutní Montáže Ostrava</t>
+          <t>Ostrava</t>
         </is>
       </c>
     </row>
@@ -51386,12 +52056,12 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = TJ Slezan Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. Patterns: TJ Slezan Frýdek-Místek (z 80/81). city Frýdek-Místek.</t>
+          <t>Frýdek-Místek = TJ Slezan Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. Patterns: TJ Slezan Frýdek-Místek (z 80/81). city Frýdek-Místek. || TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>Slezan Frýdek Místek</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -51470,12 +52140,12 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -53410,12 +54080,12 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -53857,12 +54527,12 @@
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -57356,11 +58026,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -57405,21 +58075,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0036</t>
+          <t>CLUB_S1987_88_0001</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0036 'Gumárne 1. mája Púchov' prev→CLUB_S1986_87_0083 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -57427,21 +58095,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0254</t>
+          <t>CLUB_S1987_88_0015</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0254 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -57449,21 +58115,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0255</t>
+          <t>CLUB_S1987_88_0022</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0255 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -57471,21 +58135,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0256</t>
+          <t>CLUB_S1987_88_0023</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0256 fate nekonzist. ['reorganizace', 'setrval'] → 'reorganizace' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -57493,21 +58155,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0464</t>
+          <t>CLUB_S1987_88_0024</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0464 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -57515,21 +58175,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0465</t>
+          <t>CLUB_S1987_88_0029</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0465 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -57537,21 +58195,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0466</t>
+          <t>CLUB_S1987_88_0030</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0466 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -57559,21 +58215,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0467</t>
+          <t>CLUB_S1987_88_0036</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0467 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1986_87_0083 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -57581,21 +58235,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0468</t>
+          <t>CLUB_S1987_88_0051</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0468 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -57603,21 +58255,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0469</t>
+          <t>CLUB_S1987_88_0072</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0469 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -57625,21 +58275,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0470</t>
+          <t>CLUB_S1987_88_0077</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0470 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -57647,21 +58295,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0471</t>
+          <t>CLUB_S1987_88_0078</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0471 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -57669,24 +58315,1042 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>fate</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0472</t>
+          <t>CLUB_S1987_88_0085</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0472 fate nekonzist. ['postup', 'setrval'] → 'setrval' (cross-ref=ano) — ověřit</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0098</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0099</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0135</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0171</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0174</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0175</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0175</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0177</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0181</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0189</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0193</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0203</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0204</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0206</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0207</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0219</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0251</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'JZD Stráž míru Řenče' → 'Řenče' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0266</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0272</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Stadion Cheb' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0291</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0297</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0298</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0299</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0301</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0302</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0303</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0305</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0309</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0312</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0330</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0331</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0351</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0388</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0390</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0395</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0398</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0406</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0410</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0423</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0427</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0457</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0458</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0460</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0507</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>CLUB_S1987_88_0518</t>
+        </is>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0024</t>
+        </is>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0025</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0026</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0027</t>
+        </is>
+      </c>
+      <c r="D63" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Slovensko'</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0028</t>
+        </is>
+      </c>
+      <c r="D64" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>pyramida (feeds_into)</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0029</t>
+        </is>
+      </c>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F14"/>
+  <autoFilter ref="A1:F65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1987_88_FINAL.xlsx
+++ b/data/S1987_88_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23900,7 +23900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23950,7 +23950,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -23962,7 +23962,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -23974,7 +23974,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -23986,7 +23986,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1986_87_0083 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -23998,7 +23998,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -24010,7 +24010,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -24022,7 +24022,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -24034,7 +24034,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1986_87_0083 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -24046,7 +24046,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -24058,7 +24058,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -24070,7 +24070,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -24082,7 +24082,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -24094,7 +24094,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -24106,7 +24106,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -24118,7 +24118,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -24130,7 +24130,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -24142,7 +24142,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -24166,7 +24166,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -24178,7 +24178,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -24190,7 +24190,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'JZD Stráž míru Řenče' → 'Řenče' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -24202,7 +24202,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -24214,7 +24214,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -24226,7 +24226,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -24238,7 +24238,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -24250,7 +24250,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -24262,7 +24262,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -24274,7 +24274,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -24286,7 +24286,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -24298,7 +24298,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'JZD Stráž míru Řenče' → 'Řenče' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -24310,7 +24310,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -24322,7 +24322,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Stadion Cheb' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -24334,7 +24334,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -24346,7 +24346,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -24358,7 +24358,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -24370,7 +24370,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -24382,7 +24382,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -24394,7 +24394,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -24406,7 +24406,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -24418,7 +24418,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -24430,7 +24430,7 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -24442,7 +24442,7 @@
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -24454,7 +24454,7 @@
     <row r="45">
       <c r="C45" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -24466,7 +24466,7 @@
     <row r="46">
       <c r="C46" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -24478,7 +24478,7 @@
     <row r="47">
       <c r="C47" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -24490,7 +24490,7 @@
     <row r="48">
       <c r="C48" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -24500,9 +24500,14 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0024</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -24512,9 +24517,14 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0025</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -24524,9 +24534,14 @@
       </c>
     </row>
     <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0026</t>
+        </is>
+      </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -24536,9 +24551,14 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0027</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Slovensko'</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -24548,9 +24568,14 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0028</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -24560,186 +24585,17 @@
       </c>
     </row>
     <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0029</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>NODE_S1987_88_0024</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>NODE_S1987_88_0025</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>NODE_S1987_88_0026</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>NODE_S1987_88_0027</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Slovensko'</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>NODE_S1987_88_0028</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>NODE_S1987_88_0029</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -24756,7 +24612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K148"/>
+  <dimension ref="A1:L148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24815,6 +24671,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -24857,6 +24718,11 @@
           <t>12 týmů: základ + playoff (QF/SF/finále/o místo) + o udržení. Mistr: VSŽ Košice.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -24946,6 +24812,11 @@
           <t>I.ČNHL: základ + playoff (QF/SF/finále/O 3.) + O 5.-8. + o udržení. I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -24988,6 +24859,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -25072,6 +24948,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -25114,6 +24995,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -25156,6 +25042,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -25198,6 +25089,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -25240,6 +25136,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -25282,6 +25183,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -25324,6 +25230,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -25366,6 +25277,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -25408,6 +25324,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -25450,6 +25371,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -25492,6 +25418,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -25534,6 +25465,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -25576,6 +25512,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -25618,6 +25559,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -25660,6 +25606,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0126</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -25702,6 +25653,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0020</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -25744,6 +25700,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0021</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -26025,6 +25986,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0027</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -26319,6 +26285,11 @@
           <t>II.ČNHL: 3 skupiny + finále.</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0033</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -26361,6 +26332,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0034</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -26403,6 +26379,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0035</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -26445,6 +26426,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0036</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -26487,6 +26473,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0037</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -26529,6 +26520,11 @@
           <t>II.SNHL: červená+modrá sk. + fáze.</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0038</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -26571,6 +26567,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0039</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -26613,6 +26614,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0040</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -26655,6 +26661,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0041</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -26697,6 +26708,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0042</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -26739,6 +26755,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0043</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -26781,6 +26802,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0044</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -26823,6 +26849,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0045</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -26865,6 +26896,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0046</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -26907,6 +26943,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0047</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -26949,6 +26990,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0048</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -27290,6 +27336,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0051</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -27332,6 +27383,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0055</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -27374,6 +27430,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0056</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -27416,6 +27477,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0057</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -27458,6 +27524,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0058</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -27500,6 +27571,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0059</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -27542,6 +27618,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0060</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -27589,6 +27670,11 @@
           <t>Kvalifikace o KP</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0061</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -27631,6 +27717,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0062</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -27673,6 +27764,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0063</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -27715,6 +27811,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0064</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -27757,6 +27858,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0065</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -27841,6 +27947,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0067</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -27883,6 +27994,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0068</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -27925,6 +28041,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0069</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -27972,6 +28093,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0071</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -28014,6 +28140,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0072</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -28056,6 +28187,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0073</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -28140,6 +28276,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0077</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -28182,6 +28323,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0078</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -28224,6 +28370,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0079</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -28266,6 +28417,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0080</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -28308,6 +28464,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0081</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -28350,6 +28511,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0082</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -28392,6 +28558,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0083</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -28434,6 +28605,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0084</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -28476,6 +28652,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0085</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -28518,6 +28699,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0086</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -28560,6 +28746,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0087</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -28602,6 +28793,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0088</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -28644,6 +28840,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0089</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -28686,6 +28887,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0090</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -28728,6 +28934,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0092</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -28770,6 +28981,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0093</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -29022,6 +29238,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0099</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -29064,6 +29285,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0100</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -29106,6 +29332,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0101</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -29148,6 +29379,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0102</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -29190,6 +29426,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0103</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -29316,6 +29557,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0106</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -29358,6 +29604,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0107</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -29400,6 +29651,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0108</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -29442,6 +29698,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0109</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -29489,6 +29750,11 @@
           <t>Kvalifikace o KP</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0110</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -29531,6 +29797,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0111</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -29573,6 +29844,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0112</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -29615,6 +29891,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0113</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -29783,6 +30064,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0118</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -29823,6 +30109,11 @@
       <c r="J121" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0119</t>
         </is>
       </c>
     </row>
@@ -32467,12 +32758,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -33065,12 +33356,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -33401,12 +33692,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -33695,12 +33986,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -39437,12 +39728,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -39605,12 +39896,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -39694,12 +39985,12 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -39867,12 +40158,12 @@
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -40243,12 +40534,12 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -44049,12 +44340,12 @@
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Stadion Cheb' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>Stadion Cheb</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -49179,12 +49470,12 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -52140,12 +52431,12 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -58026,7 +58317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -58080,12 +58371,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0001</t>
+          <t>CLUB_S1987_88_0022</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58100,12 +58391,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0015</t>
+          <t>CLUB_S1987_88_0024</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58120,12 +58411,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0022</t>
+          <t>CLUB_S1987_88_0029</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58140,12 +58431,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0023</t>
+          <t>CLUB_S1987_88_0036</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1986_87_0083 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -58160,12 +58451,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0024</t>
+          <t>CLUB_S1987_88_0051</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58180,12 +58471,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0029</t>
+          <t>CLUB_S1987_88_0072</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58200,12 +58491,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0030</t>
+          <t>CLUB_S1987_88_0077</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58220,12 +58511,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0036</t>
+          <t>CLUB_S1987_88_0078</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1986_87_0083 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58240,12 +58531,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0051</t>
+          <t>CLUB_S1987_88_0085</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58260,12 +58551,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0072</t>
+          <t>CLUB_S1987_88_0098</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58280,12 +58571,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0077</t>
+          <t>CLUB_S1987_88_0099</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58300,12 +58591,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0078</t>
+          <t>CLUB_S1987_88_0135</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58320,12 +58611,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0085</t>
+          <t>CLUB_S1987_88_0174</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58340,12 +58631,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0098</t>
+          <t>CLUB_S1987_88_0175</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58360,12 +58651,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0099</t>
+          <t>CLUB_S1987_88_0193</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58380,12 +58671,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0135</t>
+          <t>CLUB_S1987_88_0203</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58400,12 +58691,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0171</t>
+          <t>CLUB_S1987_88_0204</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58420,7 +58711,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0174</t>
+          <t>CLUB_S1987_88_0206</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -58440,12 +58731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0175</t>
+          <t>CLUB_S1987_88_0207</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58460,12 +58751,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0175</t>
+          <t>CLUB_S1987_88_0219</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -58480,12 +58771,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0177</t>
+          <t>CLUB_S1987_88_0251</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'JZD Stráž míru Řenče' → 'Řenče' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58500,12 +58791,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0181</t>
+          <t>CLUB_S1987_88_0266</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58520,12 +58811,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0189</t>
+          <t>CLUB_S1987_88_0291</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58540,12 +58831,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0193</t>
+          <t>CLUB_S1987_88_0297</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58560,12 +58851,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0203</t>
+          <t>CLUB_S1987_88_0298</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58580,12 +58871,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0204</t>
+          <t>CLUB_S1987_88_0299</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58600,12 +58891,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0206</t>
+          <t>CLUB_S1987_88_0301</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58620,12 +58911,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0207</t>
+          <t>CLUB_S1987_88_0302</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58640,12 +58931,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0219</t>
+          <t>CLUB_S1987_88_0303</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58660,12 +58951,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0251</t>
+          <t>CLUB_S1987_88_0305</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'JZD Stráž míru Řenče' → 'Řenče' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58680,12 +58971,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0266</t>
+          <t>CLUB_S1987_88_0309</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58700,12 +58991,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0272</t>
+          <t>CLUB_S1987_88_0312</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Stadion Cheb' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58720,12 +59011,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0291</t>
+          <t>CLUB_S1987_88_0330</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -58740,12 +59031,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0297</t>
+          <t>CLUB_S1987_88_0331</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58760,12 +59051,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0298</t>
+          <t>CLUB_S1987_88_0351</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -58780,12 +59071,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0299</t>
+          <t>CLUB_S1987_88_0388</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
     </row>
@@ -58800,12 +59091,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0301</t>
+          <t>CLUB_S1987_88_0395</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -58820,12 +59111,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0302</t>
+          <t>CLUB_S1987_88_0398</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58840,12 +59131,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0303</t>
+          <t>CLUB_S1987_88_0406</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -58860,12 +59151,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0305</t>
+          <t>CLUB_S1987_88_0410</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58880,12 +59171,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0309</t>
+          <t>CLUB_S1987_88_0423</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -58900,12 +59191,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0312</t>
+          <t>CLUB_S1987_88_0427</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58920,12 +59211,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0330</t>
+          <t>CLUB_S1987_88_0457</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58940,12 +59231,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0331</t>
+          <t>CLUB_S1987_88_0458</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58960,12 +59251,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0351</t>
+          <t>CLUB_S1987_88_0507</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58980,12 +59271,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0388</t>
+          <t>CLUB_S1987_88_0518</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58995,17 +59286,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0390</t>
+          <t>NODE_S1987_88_0024</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
     </row>
@@ -59015,17 +59306,17 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0395</t>
+          <t>NODE_S1987_88_0025</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
     </row>
@@ -59035,17 +59326,17 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0398</t>
+          <t>NODE_S1987_88_0026</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
         </is>
       </c>
     </row>
@@ -59055,17 +59346,17 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0406</t>
+          <t>NODE_S1987_88_0027</t>
         </is>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  Slovensko'</t>
         </is>
       </c>
     </row>
@@ -59075,17 +59366,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0410</t>
+          <t>NODE_S1987_88_0028</t>
         </is>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
     </row>
@@ -59095,262 +59386,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>prev_club_id / identita</t>
+          <t>pyramida (feeds_into)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CLUB_S1987_88_0423</t>
+          <t>NODE_S1987_88_0029</t>
         </is>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>CLUB_S1987_88_0427</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>CLUB_S1987_88_0457</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>CLUB_S1987_88_0458</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>CLUB_S1987_88_0460</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>CLUB_S1987_88_0507</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>CLUB_S1987_88_0518</t>
-        </is>
-      </c>
-      <c r="D59" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>NODE_S1987_88_0024</t>
-        </is>
-      </c>
-      <c r="D60" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>NODE_S1987_88_0025</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="inlineStr">
-        <is>
           <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>NODE_S1987_88_0026</t>
-        </is>
-      </c>
-      <c r="D62" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>NODE_S1987_88_0027</t>
-        </is>
-      </c>
-      <c r="D63" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  Slovensko'</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>NODE_S1987_88_0028</t>
-        </is>
-      </c>
-      <c r="D64" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>pyramida (feeds_into)</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>NODE_S1987_88_0029</t>
-        </is>
-      </c>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F65"/>
+  <autoFilter ref="A1:F53"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1987_88_FINAL.xlsx
+++ b/data/S1987_88_FINAL.xlsx
@@ -21369,7 +21369,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Krajský přebor / Družstevník Krakovany — odstoupil po 3.kole</t>
+          <t>Krajský přebor</t>
         </is>
       </c>
       <c r="C11" s="2" t="n"/>
@@ -23900,7 +23900,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D54"/>
+  <dimension ref="A1:D55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23948,21 +23948,26 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30ZASL</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] Družstevník Krakovany — odstoupil po 3.kole</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -23974,7 +23979,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -23986,7 +23991,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1986_87_0083 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -23998,7 +24003,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1986_87_0083 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -24010,7 +24015,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -24022,7 +24027,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -24034,7 +24039,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -24046,7 +24051,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -24058,7 +24063,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -24070,7 +24075,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -24082,7 +24087,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -24094,7 +24099,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -24106,7 +24111,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -24118,7 +24123,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -24130,7 +24135,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -24178,7 +24183,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -24190,7 +24195,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'JZD Stráž míru Řenče' → 'Řenče' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -24202,7 +24207,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'JZD Stráž míru Řenče' → 'Řenče' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -24214,7 +24219,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -24226,7 +24231,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -24238,7 +24243,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -24250,7 +24255,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -24262,7 +24267,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -24274,7 +24279,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -24286,7 +24291,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -24298,7 +24303,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -24334,7 +24339,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -24346,7 +24351,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -24358,7 +24363,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -24370,7 +24375,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -24382,7 +24387,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -24394,7 +24399,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -24406,7 +24411,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -24418,7 +24423,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -24430,7 +24435,7 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -24442,7 +24447,7 @@
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -24454,7 +24459,7 @@
     <row r="45">
       <c r="C45" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -24466,7 +24471,7 @@
     <row r="46">
       <c r="C46" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hutní Montáže Ostrava' → 'Ostrava' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -24478,7 +24483,7 @@
     <row r="47">
       <c r="C47" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -24500,14 +24505,9 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>NODE_S1987_88_0024</t>
-        </is>
-      </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -24519,12 +24519,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>NODE_S1987_88_0025</t>
+          <t>NODE_S1987_88_0024</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -24536,12 +24536,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NODE_S1987_88_0026</t>
+          <t>NODE_S1987_88_0025</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -24553,12 +24553,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NODE_S1987_88_0027</t>
+          <t>NODE_S1987_88_0026</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Slovensko'</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina C'</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -24570,12 +24570,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>NODE_S1987_88_0028</t>
+          <t>NODE_S1987_88_0027</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  Slovensko'</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -24587,15 +24587,32 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>NODE_S1987_88_0028</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina A'</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>NODE_S1987_88_0029</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>[TBD] pyramida (feeds_into): top-level kvalifikace bez feeds_into: 'KVAL  skupina B'</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>

--- a/data/S1987_88_FINAL.xlsx
+++ b/data/S1987_88_FINAL.xlsx
@@ -55225,10 +55225,10 @@
         <v>16</v>
       </c>
       <c r="H5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
         <v>124</v>
@@ -55242,7 +55242,7 @@
         <v>117</v>
       </c>
       <c r="M5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>

--- a/data/S1987_88_FINAL.xlsx
+++ b/data/S1987_88_FINAL.xlsx
@@ -24629,7 +24629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L148"/>
+  <dimension ref="A1:N148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24693,6 +24693,16 @@
           <t>prev_node_id</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -30685,8 +30695,6 @@
         </is>
       </c>
     </row>
-    <row r="135"/>
-    <row r="136"/>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
@@ -30786,7 +30794,6 @@
         </is>
       </c>
     </row>
-    <row r="144"/>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>

--- a/data/S1987_88_FINAL.xlsx
+++ b/data/S1987_88_FINAL.xlsx
@@ -24965,6 +24965,16 @@
           <t>NODE_S1987_88_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0008</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0014</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24979,6 +24989,14 @@
         <is>
           <t>NODE_S1986_87_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -25059,6 +25077,12 @@
           <t>NODE_S1987_88_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0009</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25073,6 +25097,14 @@
         <is>
           <t>NODE_S1986_87_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>1.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -25106,6 +25138,16 @@
           <t>NODE_S1987_88_0007</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0013</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0012</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25120,6 +25162,14 @@
         <is>
           <t>NODE_S1986_87_0009</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -25153,6 +25203,8 @@
           <t>NODE_S1987_88_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25167,6 +25219,14 @@
         <is>
           <t>NODE_S1986_87_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -25200,6 +25260,8 @@
           <t>NODE_S1987_88_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25214,6 +25276,14 @@
         <is>
           <t>NODE_S1986_87_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -25247,6 +25317,8 @@
           <t>NODE_S1987_88_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25261,6 +25333,14 @@
         <is>
           <t>NODE_S1986_87_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -25294,6 +25374,8 @@
           <t>NODE_S1987_88_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25308,6 +25390,14 @@
         <is>
           <t>NODE_S1986_87_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -25341,6 +25431,8 @@
           <t>NODE_S1987_88_0001</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25355,6 +25447,14 @@
         <is>
           <t>NODE_S1986_87_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>9.–12. ZČ</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -25388,6 +25488,8 @@
           <t>NODE_S1987_88_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25402,6 +25504,14 @@
         <is>
           <t>NODE_S1986_87_0015</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -25435,6 +25545,16 @@
           <t>NODE_S1987_88_0004</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0017</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0022</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25449,6 +25569,14 @@
         <is>
           <t>NODE_S1986_87_0016</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -25482,6 +25610,16 @@
           <t>NODE_S1987_88_0004</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0018</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0021</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25496,6 +25634,14 @@
         <is>
           <t>NODE_S1986_87_0017</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -25529,6 +25675,16 @@
           <t>NODE_S1987_88_0004</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0019</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0020</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25543,6 +25699,14 @@
         <is>
           <t>NODE_S1986_87_0018</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -25576,6 +25740,8 @@
           <t>NODE_S1987_88_0004</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25590,6 +25756,14 @@
         <is>
           <t>NODE_S1986_87_0019</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -25623,6 +25797,8 @@
           <t>NODE_S1987_88_0004</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25637,6 +25813,14 @@
         <is>
           <t>NODE_S1986_87_0126</t>
         </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="22">
@@ -25670,6 +25854,8 @@
           <t>NODE_S1987_88_0004</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25684,6 +25870,14 @@
         <is>
           <t>NODE_S1986_87_0020</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -25717,6 +25911,8 @@
           <t>NODE_S1987_88_0004</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25731,6 +25927,14 @@
         <is>
           <t>NODE_S1986_87_0021</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -26134,6 +26338,12 @@
           <t>NODE_S1987_88_0030</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0034</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26143,6 +26353,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -26176,6 +26394,8 @@
           <t>NODE_S1987_88_0030</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26185,6 +26405,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="36">
@@ -26218,6 +26446,8 @@
           <t>NODE_S1987_88_0030</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26227,6 +26457,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -26490,6 +26728,8 @@
           <t>NODE_S1987_88_0037</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26504,6 +26744,14 @@
         <is>
           <t>NODE_S1986_87_0037</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -26678,6 +26926,8 @@
           <t>NODE_S1987_88_0043</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26692,6 +26942,14 @@
         <is>
           <t>NODE_S1986_87_0041</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -26725,6 +26983,8 @@
           <t>NODE_S1987_88_0043</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26739,6 +26999,14 @@
         <is>
           <t>NODE_S1986_87_0042</t>
         </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -26772,6 +27040,8 @@
           <t>NODE_S1987_88_0044</t>
         </is>
       </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26786,6 +27056,14 @@
         <is>
           <t>NODE_S1986_87_0043</t>
         </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N48" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="49">
@@ -26819,6 +27097,8 @@
           <t>NODE_S1987_88_0044</t>
         </is>
       </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26833,6 +27113,14 @@
         <is>
           <t>NODE_S1986_87_0044</t>
         </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -26866,6 +27154,8 @@
           <t>NODE_S1987_88_0042</t>
         </is>
       </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26880,6 +27170,14 @@
         <is>
           <t>NODE_S1986_87_0045</t>
         </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N50" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -26908,6 +27206,16 @@
           <t>REG_STC</t>
         </is>
       </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0060</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0056</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26927,6 +27235,14 @@
         <is>
           <t>NODE_S1986_87_0046</t>
         </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -27180,6 +27496,8 @@
           <t>NODE_S1987_88_0050</t>
         </is>
       </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27189,6 +27507,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>3.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -27353,6 +27679,8 @@
           <t>NODE_S1987_88_0050</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27367,6 +27695,14 @@
         <is>
           <t>NODE_S1986_87_0051</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -27588,6 +27924,12 @@
           <t>NODE_S1987_88_0063</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0066</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27602,6 +27944,14 @@
         <is>
           <t>NODE_S1986_87_0059</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -27635,6 +27985,8 @@
           <t>NODE_S1987_88_0063</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27649,6 +28001,14 @@
         <is>
           <t>NODE_S1986_87_0060</t>
         </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="68">
@@ -27828,6 +28188,12 @@
           <t>NODE_S1987_88_0068</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0071</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27842,6 +28208,14 @@
         <is>
           <t>NODE_S1986_87_0064</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -27875,6 +28249,8 @@
           <t>NODE_S1987_88_0068</t>
         </is>
       </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27889,6 +28265,14 @@
         <is>
           <t>NODE_S1986_87_0065</t>
         </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N72" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="73">
@@ -27922,6 +28306,8 @@
           <t>NODE_S1987_88_0068</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27931,6 +28317,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="74">
@@ -28481,6 +28875,8 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28495,6 +28891,14 @@
         <is>
           <t>NODE_S1986_87_0081</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -28528,6 +28932,8 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28542,6 +28948,14 @@
         <is>
           <t>NODE_S1986_87_0082</t>
         </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -28575,6 +28989,8 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28589,6 +29005,14 @@
         <is>
           <t>NODE_S1986_87_0083</t>
         </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -28622,6 +29046,8 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28636,6 +29062,14 @@
         <is>
           <t>NODE_S1986_87_0084</t>
         </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -28669,6 +29103,8 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28683,6 +29119,14 @@
         <is>
           <t>NODE_S1986_87_0085</t>
         </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="90">
@@ -28716,6 +29160,8 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28730,6 +29176,14 @@
         <is>
           <t>NODE_S1986_87_0086</t>
         </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>o 11. místo</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -28763,6 +29217,8 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28777,6 +29233,14 @@
         <is>
           <t>NODE_S1986_87_0087</t>
         </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -28810,6 +29274,8 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28824,6 +29290,14 @@
         <is>
           <t>NODE_S1986_87_0088</t>
         </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="93">
@@ -28857,6 +29331,8 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28871,6 +29347,14 @@
         <is>
           <t>NODE_S1986_87_0089</t>
         </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -28904,6 +29388,8 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28918,6 +29404,14 @@
         <is>
           <t>NODE_S1986_87_0090</t>
         </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -29129,6 +29623,8 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29138,6 +29634,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -29171,6 +29675,8 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29180,6 +29686,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="101">
@@ -29213,6 +29727,8 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29222,6 +29738,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="102">
@@ -29490,6 +30014,8 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29499,6 +30025,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -29532,6 +30066,8 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29541,6 +30077,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="109">
@@ -29574,6 +30118,8 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29588,6 +30134,14 @@
         <is>
           <t>NODE_S1986_87_0106</t>
         </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -29621,6 +30175,8 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29635,6 +30191,14 @@
         <is>
           <t>NODE_S1986_87_0107</t>
         </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -29668,6 +30232,8 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29682,6 +30248,14 @@
         <is>
           <t>NODE_S1986_87_0108</t>
         </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N111" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -29715,6 +30289,8 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29729,6 +30305,14 @@
         <is>
           <t>NODE_S1986_87_0109</t>
         </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N112" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -29908,6 +30492,16 @@
           <t>NODE_S1987_88_0113</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0116</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>NODE_S1987_88_0117</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29922,6 +30516,14 @@
         <is>
           <t>NODE_S1986_87_0113</t>
         </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="117">
@@ -29955,6 +30557,8 @@
           <t>NODE_S1987_88_0113</t>
         </is>
       </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29964,6 +30568,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N117" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="118">
@@ -29997,6 +30609,8 @@
           <t>NODE_S1987_88_0113</t>
         </is>
       </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30006,6 +30620,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N118" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -30217,6 +30839,8 @@
           <t>NODE_S1987_88_0113</t>
         </is>
       </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30226,6 +30850,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N123" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="124">
@@ -30259,6 +30891,8 @@
           <t>NODE_S1987_88_0113</t>
         </is>
       </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30268,6 +30902,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N124" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="125">
@@ -30516,6 +31158,8 @@
           <t>NODE_S1987_88_0125</t>
         </is>
       </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30525,6 +31169,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N130" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -30558,6 +31210,8 @@
           <t>NODE_S1987_88_0125</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30567,6 +31221,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="132">
@@ -30600,6 +31262,8 @@
           <t>NODE_S1987_88_0125</t>
         </is>
       </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30609,6 +31273,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N132" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -30642,6 +31314,8 @@
           <t>NODE_S1987_88_0125</t>
         </is>
       </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30651,6 +31325,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N133" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="134">
@@ -30695,6 +31377,8 @@
         </is>
       </c>
     </row>
+    <row r="135"/>
+    <row r="136"/>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
@@ -30794,6 +31478,7 @@
         </is>
       </c>
     </row>
+    <row r="144"/>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>

--- a/data/S1987_88_FINAL.xlsx
+++ b/data/S1987_88_FINAL.xlsx
@@ -838,6 +838,11 @@
           <t>VSŽ Košice</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F6" t="n">
         <v>34</v>
       </c>
@@ -25082,7 +25087,6 @@
           <t>NODE_S1987_88_0009</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25203,8 +25207,6 @@
           <t>NODE_S1987_88_0007</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25260,8 +25262,6 @@
           <t>NODE_S1987_88_0007</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25317,8 +25317,6 @@
           <t>NODE_S1987_88_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25374,8 +25372,6 @@
           <t>NODE_S1987_88_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25431,8 +25427,6 @@
           <t>NODE_S1987_88_0001</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25488,8 +25482,6 @@
           <t>NODE_S1987_88_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25740,8 +25732,6 @@
           <t>NODE_S1987_88_0004</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25797,8 +25787,6 @@
           <t>NODE_S1987_88_0004</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25854,8 +25842,6 @@
           <t>NODE_S1987_88_0004</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25911,8 +25897,6 @@
           <t>NODE_S1987_88_0004</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26343,7 +26327,6 @@
           <t>NODE_S1987_88_0034</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26394,8 +26377,6 @@
           <t>NODE_S1987_88_0030</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26446,8 +26427,6 @@
           <t>NODE_S1987_88_0030</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26728,8 +26707,6 @@
           <t>NODE_S1987_88_0037</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26926,8 +26903,6 @@
           <t>NODE_S1987_88_0043</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26983,8 +26958,6 @@
           <t>NODE_S1987_88_0043</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27040,8 +27013,6 @@
           <t>NODE_S1987_88_0044</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27097,8 +27068,6 @@
           <t>NODE_S1987_88_0044</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27154,8 +27123,6 @@
           <t>NODE_S1987_88_0042</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27496,8 +27463,6 @@
           <t>NODE_S1987_88_0050</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27679,8 +27644,6 @@
           <t>NODE_S1987_88_0050</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27929,7 +27892,6 @@
           <t>NODE_S1987_88_0066</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27985,8 +27947,6 @@
           <t>NODE_S1987_88_0063</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28193,7 +28153,6 @@
           <t>NODE_S1987_88_0071</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28249,8 +28208,6 @@
           <t>NODE_S1987_88_0068</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28306,8 +28263,6 @@
           <t>NODE_S1987_88_0068</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28875,8 +28830,6 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28932,8 +28885,6 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28989,8 +28940,6 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29046,8 +28995,6 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29103,8 +29050,6 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29160,8 +29105,6 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29217,8 +29160,6 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29274,8 +29215,6 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29331,8 +29270,6 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29388,8 +29325,6 @@
           <t>NODE_S1987_88_0081</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29623,8 +29558,6 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29675,8 +29608,6 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29727,8 +29658,6 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30014,8 +29943,6 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30066,8 +29993,6 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30118,8 +30043,6 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30175,8 +30098,6 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30232,8 +30153,6 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr"/>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30289,8 +30208,6 @@
           <t>NODE_S1987_88_0094</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr"/>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30557,8 +30474,6 @@
           <t>NODE_S1987_88_0113</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr"/>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30609,8 +30524,6 @@
           <t>NODE_S1987_88_0113</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30839,8 +30752,6 @@
           <t>NODE_S1987_88_0113</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr"/>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -30891,8 +30802,6 @@
           <t>NODE_S1987_88_0113</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr"/>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -31158,8 +31067,6 @@
           <t>NODE_S1987_88_0125</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr"/>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -31210,8 +31117,6 @@
           <t>NODE_S1987_88_0125</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -31262,8 +31167,6 @@
           <t>NODE_S1987_88_0125</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr"/>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -31314,8 +31217,6 @@
           <t>NODE_S1987_88_0125</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr"/>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -31377,8 +31278,6 @@
         </is>
       </c>
     </row>
-    <row r="135"/>
-    <row r="136"/>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
@@ -31478,7 +31377,6 @@
         </is>
       </c>
     </row>
-    <row r="144"/>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
@@ -58820,7 +58718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59012,6 +58910,18 @@
       <c r="B16" t="inlineStr">
         <is>
           <t>0 oprav kvalifikačních levelů. Sloupec Q (level) aktualizován.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>VSŽ Košice</t>
         </is>
       </c>
     </row>

--- a/data/S1987_88_FINAL.xlsx
+++ b/data/S1987_88_FINAL.xlsx
@@ -66006,7 +66006,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="M10" t="n">
         <v>2</v>

--- a/data/S1987_88_FINAL.xlsx
+++ b/data/S1987_88_FINAL.xlsx
@@ -31278,6 +31278,8 @@
         </is>
       </c>
     </row>
+    <row r="135"/>
+    <row r="136"/>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
@@ -31377,6 +31379,7 @@
         </is>
       </c>
     </row>
+    <row r="144"/>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
